--- a/artfynd/A 32574-2025 artfynd.xlsx
+++ b/artfynd/A 32574-2025 artfynd.xlsx
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126500441</v>
+        <v>126501774</v>
       </c>
       <c r="B7" t="n">
-        <v>98278</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504143</v>
+        <v>504116</v>
       </c>
       <c r="R7" t="n">
-        <v>6850036</v>
+        <v>6850171</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126501774</v>
+        <v>126500441</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504116</v>
+        <v>504143</v>
       </c>
       <c r="R8" t="n">
-        <v>6850171</v>
+        <v>6850036</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
